--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62034.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62034.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,21 +721,15 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -746,10 +740,21 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62034.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62034.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yp</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DCNL</t>
+          <t>A NIGIK</t>
         </is>
       </c>
     </row>
